--- a/selenium/Python_data.xlsx
+++ b/selenium/Python_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Class_Lavanya\selenium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968E37A6-5D7A-40B9-95AC-9A537F13CAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924B928E-6910-4B63-96B7-64874536523B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A05D6E44-CB7A-413B-8FBA-F4A38C869CC3}"/>
+    <workbookView xWindow="3948" yWindow="696" windowWidth="17280" windowHeight="8880" xr2:uid="{A05D6E44-CB7A-413B-8FBA-F4A38C869CC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>firstname</t>
   </si>
@@ -52,16 +52,87 @@
   </si>
   <si>
     <t>Testcase1</t>
+  </si>
+  <si>
+    <t>Testcase2</t>
+  </si>
+  <si>
+    <t>Testcase3</t>
+  </si>
+  <si>
+    <t>Testcase4</t>
+  </si>
+  <si>
+    <t>Testcase5</t>
+  </si>
+  <si>
+    <t>Vino</t>
+  </si>
+  <si>
+    <t>babu</t>
+  </si>
+  <si>
+    <t>ram</t>
+  </si>
+  <si>
+    <t>raja</t>
+  </si>
+  <si>
+    <t>raju</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>v@gmail.com</t>
+  </si>
+  <si>
+    <t>b@gmail.com</t>
+  </si>
+  <si>
+    <t>r@gmail.com</t>
+  </si>
+  <si>
+    <t>raja@gmail.com</t>
+  </si>
+  <si>
+    <t>ru@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -75,7 +146,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,14 +154,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -403,34 +493,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BFDE96-BF40-4F51-9673-F8DFF2CDFE0F}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{474F7B19-D3FE-4294-835A-492B9CC82B84}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{E9A6F4BD-AFA7-400D-AB6D-E50DD6877B05}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{02D4892D-58F9-4071-901B-2F895A2E7E76}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{BF34E2EE-7D31-48CE-A44D-70EED9C57FA5}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{DB8E2D39-6864-47D8-BFD5-43AAF2569723}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>